--- a/outputs/Block2_National_Nested_OOF_v12.xlsx
+++ b/outputs/Block2_National_Nested_OOF_v12.xlsx
@@ -2187,7 +2187,7 @@
         <v>50</v>
       </c>
       <c r="I44">
-        <v>0.4773119999999992</v>
+        <v>0.4773119999999993</v>
       </c>
       <c r="J44">
         <v>0.4815039999999993</v>
@@ -4128,7 +4128,7 @@
         <v>0.490967999999999</v>
       </c>
       <c r="J95">
-        <v>0.487575999999999</v>
+        <v>0.4875759999999989</v>
       </c>
       <c r="K95">
         <v>0.5015465217139654</v>
@@ -5420,7 +5420,7 @@
         <v>0.4821079999999993</v>
       </c>
       <c r="J129">
-        <v>0.4865799999999994</v>
+        <v>0.4865799999999995</v>
       </c>
       <c r="K129">
         <v>0.4693095837053707</v>
